--- a/corr_matrix/residual_exam2B_1PL.xlsx
+++ b/corr_matrix/residual_exam2B_1PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2B01</t>
@@ -520,49 +525,49 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01932647756157444</v>
+        <v>-0.01930865380971086</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.09047429052744396</v>
+        <v>-0.09047145173801309</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3383893941866217</v>
+        <v>-0.3383829016553149</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2666396533123256</v>
+        <v>-0.2666361293212273</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06019727487333572</v>
+        <v>0.06020248995336131</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02143536380910929</v>
+        <v>-0.02143273268592094</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04059400278400856</v>
+        <v>-0.04060342896274134</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02600424176553981</v>
+        <v>0.02600815897126347</v>
       </c>
       <c r="K2" t="n">
-        <v>0.114001894401631</v>
+        <v>0.1139965182241591</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.01350178400677721</v>
+        <v>-0.01351664162048146</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07125591355671879</v>
+        <v>-0.07125177766422053</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.09162949605006758</v>
+        <v>-0.09164244644666722</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.07618788311489648</v>
+        <v>-0.07620363227381255</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1799357696995722</v>
+        <v>-0.1799245978185016</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2396563821018932</v>
+        <v>-0.2396486437927749</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +577,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.01932647756157444</v>
+        <v>-0.01930865380971086</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02392270657054817</v>
+        <v>0.02391974090830135</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.244341524815219</v>
+        <v>-0.2443358220939372</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.08859928522647678</v>
+        <v>-0.08859713566973972</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.08959741329829522</v>
+        <v>-0.08959086416439099</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.04542318480325613</v>
+        <v>-0.04542083450982624</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1518999307152599</v>
+        <v>-0.1519078247297299</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1135990172567945</v>
+        <v>0.1135983363604343</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.239833215552699</v>
+        <v>-0.2398440459330666</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06902664916471919</v>
+        <v>0.06900778982671173</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1801011003669618</v>
+        <v>-0.1800976278913627</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000719056661758266</v>
+        <v>0.0007066626743214572</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.06812132537699923</v>
+        <v>-0.06813763098470348</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1123104320888157</v>
+        <v>-0.1122998229373785</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3371998346536022</v>
+        <v>-0.3371904033451248</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +632,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09047429052744396</v>
+        <v>-0.09047145173801309</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02392270657054817</v>
+        <v>0.02391974090830135</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.05891483144902284</v>
+        <v>-0.05890511818953931</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1741674653631592</v>
+        <v>0.1741754693932961</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1915117738096113</v>
+        <v>-0.1915047547805027</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2046101678190547</v>
+        <v>-0.2045871861217802</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1182167180859648</v>
+        <v>-0.1181944829421833</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.06141365109473571</v>
+        <v>-0.06139721705683939</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02916179874862838</v>
+        <v>0.02915247960806565</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2255275131291727</v>
+        <v>0.2255325521137519</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1675157585745934</v>
+        <v>-0.1675074601709075</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03000381547342645</v>
+        <v>0.02999432545964024</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.07218258871827024</v>
+        <v>-0.07221435090138531</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3213001990439738</v>
+        <v>-0.3212942619212439</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.02656130422036447</v>
+        <v>-0.02655668163502421</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +687,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3383893941866217</v>
+        <v>-0.3383829016553149</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.244341524815219</v>
+        <v>-0.2443358220939372</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.05891483144902284</v>
+        <v>-0.05890511818953931</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1730908488472988</v>
+        <v>0.1730884307763329</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3282491511873785</v>
+        <v>-0.328254679160368</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03069794188782376</v>
+        <v>-0.03069172199031184</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01754181332849492</v>
+        <v>-0.01753986164951188</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3886764519087383</v>
+        <v>-0.3886675288310696</v>
       </c>
       <c r="K5" t="n">
-        <v>0.14342956672672</v>
+        <v>0.1434285734013572</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03202972613909807</v>
+        <v>0.03203106985821361</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.06567840371216296</v>
+        <v>-0.0656791868884377</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07609282159295952</v>
+        <v>0.07607862018328786</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01402485376822901</v>
+        <v>-0.01404877519019945</v>
       </c>
       <c r="P5" t="n">
-        <v>2.409795492502829e-05</v>
+        <v>1.965406310489524e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2718499006614253</v>
+        <v>0.2718487653875896</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +742,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2666396533123256</v>
+        <v>-0.2666361293212273</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.08859928522647678</v>
+        <v>-0.08859713566973972</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1741674653631592</v>
+        <v>0.1741754693932961</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1730908488472988</v>
+        <v>0.1730884307763329</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1800375583019334</v>
+        <v>-0.1800422974468582</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2888669877674163</v>
+        <v>-0.2888588580859164</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1968277393222291</v>
+        <v>-0.1968218000562486</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1695141487174448</v>
+        <v>-0.1695053999311331</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1608438016661119</v>
+        <v>0.1608364806693187</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05191554257057898</v>
+        <v>0.0519148992449875</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1372709077251163</v>
+        <v>-0.1372727829138143</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.03417732120930211</v>
+        <v>-0.03419723519136872</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01404848924678867</v>
+        <v>-0.01407857901184465</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06397975212524926</v>
+        <v>0.06397483323989694</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.05792631378015724</v>
+        <v>-0.05793016085759873</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +797,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06019727487333572</v>
+        <v>0.06020248995336131</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.08959741329829522</v>
+        <v>-0.08959086416439099</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1915117738096113</v>
+        <v>-0.1915047547805027</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3282491511873785</v>
+        <v>-0.328254679160368</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1800375583019334</v>
+        <v>-0.1800422974468582</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0259098550132629</v>
+        <v>-0.0259109951119276</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05632561004635442</v>
+        <v>-0.05633120358437902</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.09947553207507656</v>
+        <v>-0.09947018096540064</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1010460735647089</v>
+        <v>-0.1010496223967614</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2044135463250562</v>
+        <v>-0.2044181124936588</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08916899649580019</v>
+        <v>0.08916956465032162</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07029065103098106</v>
+        <v>0.07027599183269037</v>
       </c>
       <c r="O7" t="n">
-        <v>0.09031284097428834</v>
+        <v>0.09029425615889389</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1260310744116562</v>
+        <v>0.1260291270420101</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2362822019707362</v>
+        <v>-0.2362883730506849</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +852,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.02143536380910929</v>
+        <v>-0.02143273268592094</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.04542318480325613</v>
+        <v>-0.04542083450982624</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2046101678190547</v>
+        <v>-0.2045871861217802</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.03069794188782376</v>
+        <v>-0.03069172199031184</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2888669877674163</v>
+        <v>-0.2888588580859164</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0259098550132629</v>
+        <v>-0.0259109951119276</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2945790974049468</v>
+        <v>0.2945845842782304</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1181288603410174</v>
+        <v>0.118144994303603</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1253819249338718</v>
+        <v>-0.1253686161187046</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2232860265579323</v>
+        <v>-0.2232753387550395</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0252469078766961</v>
+        <v>-0.0252302019733397</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3199604427531355</v>
+        <v>-0.3199591086418643</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1582494090550289</v>
+        <v>-0.1582584047285658</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2337114464381583</v>
+        <v>-0.2337078150003693</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0766816178376758</v>
+        <v>-0.07668770031762775</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +907,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.04059400278400856</v>
+        <v>-0.04060342896274134</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1518999307152599</v>
+        <v>-0.1519078247297299</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1182167180859648</v>
+        <v>-0.1181944829421833</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.01754181332849492</v>
+        <v>-0.01753986164951188</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1968277393222291</v>
+        <v>-0.1968218000562486</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.05632561004635442</v>
+        <v>-0.05633120358437902</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2945790974049468</v>
+        <v>0.2945845842782304</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1296495013564389</v>
+        <v>-0.1296372339028895</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2220748610218728</v>
+        <v>-0.2220656938110376</v>
       </c>
       <c r="L9" t="n">
-        <v>0.164336123185005</v>
+        <v>0.1643611142970222</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.01997352069002266</v>
+        <v>-0.01996277566321347</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3537713161104932</v>
+        <v>-0.3537625588141546</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01870322336224744</v>
+        <v>0.01869270672839372</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1045117490889532</v>
+        <v>-0.1045185577166378</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.06167378899489048</v>
+        <v>-0.06168056662019195</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +962,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02600424176553981</v>
+        <v>0.02600815897126347</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1135990172567945</v>
+        <v>0.1135983363604343</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.06141365109473571</v>
+        <v>-0.06139721705683939</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3886764519087383</v>
+        <v>-0.3886675288310696</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1695141487174448</v>
+        <v>-0.1695053999311331</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.09947553207507656</v>
+        <v>-0.09947018096540064</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1181288603410174</v>
+        <v>0.118144994303603</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1296495013564389</v>
+        <v>-0.1296372339028895</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.06874960313190807</v>
+        <v>0.06873993654373876</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.02534544603053253</v>
+        <v>-0.02534369871384128</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02717348578288682</v>
+        <v>0.0271780710414773</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2379656492799627</v>
+        <v>-0.2379824173270063</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1644698532458049</v>
+        <v>-0.1645019021074005</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1202252843817589</v>
+        <v>-0.1202206837915211</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1471136725477102</v>
+        <v>-0.1471097055663321</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1017,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.114001894401631</v>
+        <v>0.1139965182241591</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.239833215552699</v>
+        <v>-0.2398440459330666</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02916179874862838</v>
+        <v>0.02915247960806565</v>
       </c>
       <c r="E11" t="n">
-        <v>0.14342956672672</v>
+        <v>0.1434285734013572</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1608438016661119</v>
+        <v>0.1608364806693187</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1010460735647089</v>
+        <v>-0.1010496223967614</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1253819249338718</v>
+        <v>-0.1253686161187046</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2220748610218728</v>
+        <v>-0.2220656938110376</v>
       </c>
       <c r="J11" t="n">
-        <v>0.06874960313190807</v>
+        <v>0.06873993654373876</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2133306283296471</v>
+        <v>-0.213330552200111</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1369869242554455</v>
+        <v>-0.1370030201237404</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.03743043524044951</v>
+        <v>-0.03745422860115279</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.02615730823785377</v>
+        <v>-0.02617746932825495</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2011607826529113</v>
+        <v>-0.2011718146514364</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.09733497836272231</v>
+        <v>0.09734008380018225</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1072,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.01350178400677721</v>
+        <v>-0.01351664162048146</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06902664916471919</v>
+        <v>0.06900778982671173</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2255275131291727</v>
+        <v>0.2255325521137519</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03202972613909807</v>
+        <v>0.03203106985821361</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05191554257057898</v>
+        <v>0.0519148992449875</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2044135463250562</v>
+        <v>-0.2044181124936588</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2232860265579323</v>
+        <v>-0.2232753387550395</v>
       </c>
       <c r="I12" t="n">
-        <v>0.164336123185005</v>
+        <v>0.1643611142970222</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.02534544603053253</v>
+        <v>-0.02534369871384128</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2133306283296471</v>
+        <v>-0.213330552200111</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.06292470980124905</v>
+        <v>-0.0629182757093785</v>
       </c>
       <c r="N12" t="n">
-        <v>0.06191769667214966</v>
+        <v>0.06192522764406237</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.193637527837315</v>
+        <v>-0.1936376179790086</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1674001765679409</v>
+        <v>-0.1674077273572103</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2750772599556591</v>
+        <v>-0.2750814558494019</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1127,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.07125591355671879</v>
+        <v>-0.07125177766422053</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1801011003669618</v>
+        <v>-0.1800976278913627</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1675157585745934</v>
+        <v>-0.1675074601709075</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.06567840371216296</v>
+        <v>-0.0656791868884377</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1372709077251163</v>
+        <v>-0.1372727829138143</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08916899649580019</v>
+        <v>0.08916956465032162</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0252469078766961</v>
+        <v>-0.0252302019733397</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.01997352069002266</v>
+        <v>-0.01996277566321347</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02717348578288682</v>
+        <v>0.0271780710414773</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1369869242554455</v>
+        <v>-0.1370030201237404</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.06292470980124905</v>
+        <v>-0.0629182757093785</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.01566493931485554</v>
+        <v>0.01564701952270637</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.07688895429408012</v>
+        <v>-0.0769199549019739</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.04795961502537929</v>
+        <v>-0.04796343970190069</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1031596295626281</v>
+        <v>-0.1031564073434476</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1182,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.09162949605006758</v>
+        <v>-0.09164244644666722</v>
       </c>
       <c r="C14" t="n">
-        <v>0.000719056661758266</v>
+        <v>0.0007066626743214572</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03000381547342645</v>
+        <v>0.02999432545964024</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07609282159295952</v>
+        <v>0.07607862018328786</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.03417732120930211</v>
+        <v>-0.03419723519136872</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07029065103098106</v>
+        <v>0.07027599183269037</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3199604427531355</v>
+        <v>-0.3199591086418643</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3537713161104932</v>
+        <v>-0.3537625588141546</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2379656492799627</v>
+        <v>-0.2379824173270063</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.03743043524044951</v>
+        <v>-0.03745422860115279</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06191769667214966</v>
+        <v>0.06192522764406237</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01566493931485554</v>
+        <v>0.01564701952270637</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1372206090131864</v>
+        <v>0.1372039269607462</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.01351882105377599</v>
+        <v>-0.0135405021281302</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1077667948863114</v>
+        <v>0.1077589236175302</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1237,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.07618788311489648</v>
+        <v>-0.07620363227381255</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.06812132537699923</v>
+        <v>-0.06813763098470348</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.07218258871827024</v>
+        <v>-0.07221435090138531</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01402485376822901</v>
+        <v>-0.01404877519019945</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.01404848924678867</v>
+        <v>-0.01407857901184465</v>
       </c>
       <c r="G15" t="n">
-        <v>0.09031284097428834</v>
+        <v>0.09029425615889389</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1582494090550289</v>
+        <v>-0.1582584047285658</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01870322336224744</v>
+        <v>0.01869270672839372</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1644698532458049</v>
+        <v>-0.1645019021074005</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.02615730823785377</v>
+        <v>-0.02617746932825495</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.193637527837315</v>
+        <v>-0.1936376179790086</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.07688895429408012</v>
+        <v>-0.0769199549019739</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1372206090131864</v>
+        <v>0.1372039269607462</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1102655299173369</v>
+        <v>0.1102396881306789</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0520295034402285</v>
+        <v>0.05202179735072979</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1292,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1799357696995722</v>
+        <v>-0.1799245978185016</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1123104320888157</v>
+        <v>-0.1122998229373785</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3213001990439738</v>
+        <v>-0.3212942619212439</v>
       </c>
       <c r="E16" t="n">
-        <v>2.409795492502829e-05</v>
+        <v>1.965406310489524e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>0.06397975212524926</v>
+        <v>0.06397483323989694</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1260310744116562</v>
+        <v>0.1260291270420101</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2337114464381583</v>
+        <v>-0.2337078150003693</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1045117490889532</v>
+        <v>-0.1045185577166378</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1202252843817589</v>
+        <v>-0.1202206837915211</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2011607826529113</v>
+        <v>-0.2011718146514364</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1674001765679409</v>
+        <v>-0.1674077273572103</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.04795961502537929</v>
+        <v>-0.04796343970190069</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.01351882105377599</v>
+        <v>-0.0135405021281302</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1102655299173369</v>
+        <v>0.1102396881306789</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1104156523531137</v>
+        <v>0.1104162945114745</v>
       </c>
     </row>
     <row r="17">
@@ -1342,49 +1347,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2396563821018932</v>
+        <v>-0.2396486437927749</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.3371998346536022</v>
+        <v>-0.3371904033451248</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.02656130422036447</v>
+        <v>-0.02655668163502421</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2718499006614253</v>
+        <v>0.2718487653875896</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.05792631378015724</v>
+        <v>-0.05793016085759873</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2362822019707362</v>
+        <v>-0.2362883730506849</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0766816178376758</v>
+        <v>-0.07668770031762775</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.06167378899489048</v>
+        <v>-0.06168056662019195</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1471136725477102</v>
+        <v>-0.1471097055663321</v>
       </c>
       <c r="K17" t="n">
-        <v>0.09733497836272231</v>
+        <v>0.09734008380018225</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2750772599556591</v>
+        <v>-0.2750814558494019</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1031596295626281</v>
+        <v>-0.1031564073434476</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1077667948863114</v>
+        <v>0.1077589236175302</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0520295034402285</v>
+        <v>0.05202179735072979</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1104156523531137</v>
+        <v>0.1104162945114745</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>

--- a/corr_matrix/residual_exam2B_1PL.xlsx
+++ b/corr_matrix/residual_exam2B_1PL.xlsx
@@ -1,37 +1,96 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
+  <si>
+    <t>2B01</t>
+  </si>
+  <si>
+    <t>2B02</t>
+  </si>
+  <si>
+    <t>2B03</t>
+  </si>
+  <si>
+    <t>2B04</t>
+  </si>
+  <si>
+    <t>2B05</t>
+  </si>
+  <si>
+    <t>2B06</t>
+  </si>
+  <si>
+    <t>2B07</t>
+  </si>
+  <si>
+    <t>2B08</t>
+  </si>
+  <si>
+    <t>2B09</t>
+  </si>
+  <si>
+    <t>2B10</t>
+  </si>
+  <si>
+    <t>2B11</t>
+  </si>
+  <si>
+    <t>2B12</t>
+  </si>
+  <si>
+    <t>2B13</t>
+  </si>
+  <si>
+    <t>2B14</t>
+  </si>
+  <si>
+    <t>2B15</t>
+  </si>
+  <si>
+    <t>2B16</t>
+  </si>
+  <si>
+    <t>question_id</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +105,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,982 +421,912 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>question_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2B01</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>2B02</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>2B03</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>2B04</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2B05</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2B06</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>2B07</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>2B08</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>2B09</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2B10</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>2B11</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>2B12</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>2B13</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>2B14</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>2B15</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>2B16</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>2B01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:17">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>-0.01930865380971086</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>-0.09047145173801309</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>-0.3383829016553149</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>-0.2666361293212273</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0.06020248995336131</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>-0.02143273268592094</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>-0.04060342896274134</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0.02600815897126347</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>0.1139965182241591</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>-0.01351664162048146</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>-0.07125177766422053</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>-0.09164244644666722</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>-0.07620363227381255</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>-0.1799245978185016</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>-0.2396486437927749</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>2B02</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:17">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
         <v>-0.01930865380971086</v>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.02391974090830135</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0.02391974090830137</v>
+      </c>
+      <c r="E3">
         <v>-0.2443358220939372</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>-0.08859713566973972</v>
       </c>
-      <c r="G3" t="n">
-        <v>-0.08959086416439099</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="G3">
+        <v>-0.08959086416439097</v>
+      </c>
+      <c r="H3">
         <v>-0.04542083450982624</v>
       </c>
-      <c r="I3" t="n">
-        <v>-0.1519078247297299</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.1135983363604343</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="I3">
+        <v>-0.1519078247297298</v>
+      </c>
+      <c r="J3">
+        <v>0.1135983363604344</v>
+      </c>
+      <c r="K3">
         <v>-0.2398440459330666</v>
       </c>
-      <c r="L3" t="n">
-        <v>0.06900778982671173</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="L3">
+        <v>0.06900778982671174</v>
+      </c>
+      <c r="M3">
         <v>-0.1800976278913627</v>
       </c>
-      <c r="N3" t="n">
-        <v>0.0007066626743214572</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="N3">
+        <v>0.0007066626743214484</v>
+      </c>
+      <c r="O3">
         <v>-0.06813763098470348</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>-0.1122998229373785</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>-0.3371904033451248</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>2B03</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:17">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
         <v>-0.09047145173801309</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.02391974090830135</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.05890511818953931</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.1741754693932961</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="C4">
+        <v>0.02391974090830137</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>-0.05890511818953927</v>
+      </c>
+      <c r="F4">
+        <v>0.174175469393296</v>
+      </c>
+      <c r="G4">
         <v>-0.1915047547805027</v>
       </c>
-      <c r="H4" t="n">
-        <v>-0.2045871861217802</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="H4">
+        <v>-0.2045871861217801</v>
+      </c>
+      <c r="I4">
         <v>-0.1181944829421833</v>
       </c>
-      <c r="J4" t="n">
-        <v>-0.06139721705683939</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.02915247960806565</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="J4">
+        <v>-0.06139721705683938</v>
+      </c>
+      <c r="K4">
+        <v>0.02915247960806563</v>
+      </c>
+      <c r="L4">
         <v>0.2255325521137519</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>-0.1675074601709075</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>0.02999432545964024</v>
       </c>
-      <c r="O4" t="n">
-        <v>-0.07221435090138531</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="O4">
+        <v>-0.0722143509013853</v>
+      </c>
+      <c r="P4">
         <v>-0.3212942619212439</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-0.02655668163502421</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>2B04</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="Q4">
+        <v>-0.02655668163502419</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
         <v>-0.3383829016553149</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>-0.2443358220939372</v>
       </c>
-      <c r="D5" t="n">
-        <v>-0.05890511818953931</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="D5">
+        <v>-0.05890511818953927</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>0.1730884307763329</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>-0.328254679160368</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>-0.03069172199031184</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>-0.01753986164951188</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>-0.3886675288310696</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>0.1434285734013572</v>
       </c>
-      <c r="L5" t="n">
-        <v>0.03203106985821361</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-0.0656791868884377</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5">
+        <v>0.03203106985821359</v>
+      </c>
+      <c r="M5">
+        <v>-0.06567918688843771</v>
+      </c>
+      <c r="N5">
         <v>0.07607862018328786</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>-0.01404877519019945</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.965406310489524e-05</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="P5">
+        <v>1.965406310489524E-05</v>
+      </c>
+      <c r="Q5">
         <v>0.2718487653875896</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>2B05</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:17">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
         <v>-0.2666361293212273</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>-0.08859713566973972</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.1741754693932961</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6">
+        <v>0.174175469393296</v>
+      </c>
+      <c r="E6">
         <v>0.1730884307763329</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>-0.1800422974468582</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>-0.2888588580859164</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>-0.1968218000562486</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>-0.1695053999311331</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>0.1608364806693187</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>0.0519148992449875</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>-0.1372727829138143</v>
       </c>
-      <c r="N6" t="n">
-        <v>-0.03419723519136872</v>
-      </c>
-      <c r="O6" t="n">
+      <c r="N6">
+        <v>-0.03419723519136873</v>
+      </c>
+      <c r="O6">
         <v>-0.01407857901184465</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>0.06397483323989694</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>-0.05793016085759873</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>2B06</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:17">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
         <v>0.06020248995336131</v>
       </c>
-      <c r="C7" t="n">
-        <v>-0.08959086416439099</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C7">
+        <v>-0.08959086416439097</v>
+      </c>
+      <c r="D7">
         <v>-0.1915047547805027</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>-0.328254679160368</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>-0.1800422974468582</v>
       </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>-0.0259109951119276</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>-0.05633120358437902</v>
       </c>
-      <c r="J7" t="n">
-        <v>-0.09947018096540064</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="J7">
+        <v>-0.09947018096540061</v>
+      </c>
+      <c r="K7">
         <v>-0.1010496223967614</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>-0.2044181124936588</v>
       </c>
-      <c r="M7" t="n">
-        <v>0.08916956465032162</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="M7">
+        <v>0.08916956465032165</v>
+      </c>
+      <c r="N7">
         <v>0.07027599183269037</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>0.09029425615889389</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>0.1260291270420101</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7">
         <v>-0.2362883730506849</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>2B07</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:17">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
         <v>-0.02143273268592094</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>-0.04542083450982624</v>
       </c>
-      <c r="D8" t="n">
-        <v>-0.2045871861217802</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8">
+        <v>-0.2045871861217801</v>
+      </c>
+      <c r="E8">
         <v>-0.03069172199031184</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>-0.2888588580859164</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>-0.0259109951119276</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <v>0.2945845842782304</v>
       </c>
-      <c r="J8" t="n">
-        <v>0.118144994303603</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="J8">
+        <v>0.1181449943036031</v>
+      </c>
+      <c r="K8">
         <v>-0.1253686161187046</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>-0.2232753387550395</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>-0.0252302019733397</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>-0.3199591086418643</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>-0.1582584047285658</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>-0.2337078150003693</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8">
         <v>-0.07668770031762775</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>2B08</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:17">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
         <v>-0.04060342896274134</v>
       </c>
-      <c r="C9" t="n">
-        <v>-0.1519078247297299</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C9">
+        <v>-0.1519078247297298</v>
+      </c>
+      <c r="D9">
         <v>-0.1181944829421833</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>-0.01753986164951188</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>-0.1968218000562486</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>-0.05633120358437902</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>0.2945845842782304</v>
       </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-0.1296372339028895</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>-0.1296372339028896</v>
+      </c>
+      <c r="K9">
         <v>-0.2220656938110376</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>0.1643611142970222</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>-0.01996277566321347</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>-0.3537625588141546</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>0.01869270672839372</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>-0.1045185577166378</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9">
         <v>-0.06168056662019195</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2B09</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:17">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
         <v>0.02600815897126347</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.1135983363604343</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.06139721705683939</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="C10">
+        <v>0.1135983363604344</v>
+      </c>
+      <c r="D10">
+        <v>-0.06139721705683938</v>
+      </c>
+      <c r="E10">
         <v>-0.3886675288310696</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>-0.1695053999311331</v>
       </c>
-      <c r="G10" t="n">
-        <v>-0.09947018096540064</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.118144994303603</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.1296372339028895</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="G10">
+        <v>-0.09947018096540061</v>
+      </c>
+      <c r="H10">
+        <v>0.1181449943036031</v>
+      </c>
+      <c r="I10">
+        <v>-0.1296372339028896</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
         <v>0.06873993654373876</v>
       </c>
-      <c r="L10" t="n">
-        <v>-0.02534369871384128</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.0271780710414773</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="L10">
+        <v>-0.02534369871384127</v>
+      </c>
+      <c r="M10">
+        <v>0.02717807104147725</v>
+      </c>
+      <c r="N10">
         <v>-0.2379824173270063</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>-0.1645019021074005</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>-0.1202206837915211</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10">
         <v>-0.1471097055663321</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>2B10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:17">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
         <v>0.1139965182241591</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>-0.2398440459330666</v>
       </c>
-      <c r="D11" t="n">
-        <v>0.02915247960806565</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11">
+        <v>0.02915247960806563</v>
+      </c>
+      <c r="E11">
         <v>0.1434285734013572</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>0.1608364806693187</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>-0.1010496223967614</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>-0.1253686161187046</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>-0.2220656938110376</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>0.06873993654373876</v>
       </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
         <v>-0.213330552200111</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>-0.1370030201237404</v>
       </c>
-      <c r="N11" t="n">
-        <v>-0.03745422860115279</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="N11">
+        <v>-0.03745422860115281</v>
+      </c>
+      <c r="O11">
         <v>-0.02617746932825495</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>-0.2011718146514364</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11">
         <v>0.09734008380018225</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2B11</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:17">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
         <v>-0.01351664162048146</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.06900778982671173</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12">
+        <v>0.06900778982671174</v>
+      </c>
+      <c r="D12">
         <v>0.2255325521137519</v>
       </c>
-      <c r="E12" t="n">
-        <v>0.03203106985821361</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="E12">
+        <v>0.03203106985821359</v>
+      </c>
+      <c r="F12">
         <v>0.0519148992449875</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>-0.2044181124936588</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>-0.2232753387550395</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>0.1643611142970222</v>
       </c>
-      <c r="J12" t="n">
-        <v>-0.02534369871384128</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J12">
+        <v>-0.02534369871384127</v>
+      </c>
+      <c r="K12">
         <v>-0.213330552200111</v>
       </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
         <v>-0.0629182757093785</v>
       </c>
-      <c r="N12" t="n">
-        <v>0.06192522764406237</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="N12">
+        <v>0.06192522764406233</v>
+      </c>
+      <c r="O12">
         <v>-0.1936376179790086</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>-0.1674077273572103</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12">
         <v>-0.2750814558494019</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>2B12</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:17">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
         <v>-0.07125177766422053</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>-0.1800976278913627</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>-0.1675074601709075</v>
       </c>
-      <c r="E13" t="n">
-        <v>-0.0656791868884377</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="E13">
+        <v>-0.06567918688843771</v>
+      </c>
+      <c r="F13">
         <v>-0.1372727829138143</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.08916956465032162</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="G13">
+        <v>0.08916956465032165</v>
+      </c>
+      <c r="H13">
         <v>-0.0252302019733397</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>-0.01996277566321347</v>
       </c>
-      <c r="J13" t="n">
-        <v>0.0271780710414773</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="J13">
+        <v>0.02717807104147725</v>
+      </c>
+      <c r="K13">
         <v>-0.1370030201237404</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>-0.0629182757093785</v>
       </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.01564701952270637</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>0.01564701952270635</v>
+      </c>
+      <c r="O13">
         <v>-0.0769199549019739</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13">
         <v>-0.04796343970190069</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13">
         <v>-0.1031564073434476</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>2B13</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:17">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14">
         <v>-0.09164244644666722</v>
       </c>
-      <c r="C14" t="n">
-        <v>0.0007066626743214572</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="C14">
+        <v>0.0007066626743214484</v>
+      </c>
+      <c r="D14">
         <v>0.02999432545964024</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>0.07607862018328786</v>
       </c>
-      <c r="F14" t="n">
-        <v>-0.03419723519136872</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="F14">
+        <v>-0.03419723519136873</v>
+      </c>
+      <c r="G14">
         <v>0.07027599183269037</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>-0.3199591086418643</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>-0.3537625588141546</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>-0.2379824173270063</v>
       </c>
-      <c r="K14" t="n">
-        <v>-0.03745422860115279</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.06192522764406237</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.01564701952270637</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="K14">
+        <v>-0.03745422860115281</v>
+      </c>
+      <c r="L14">
+        <v>0.06192522764406233</v>
+      </c>
+      <c r="M14">
+        <v>0.01564701952270635</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
         <v>0.1372039269607462</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14">
         <v>-0.0135405021281302</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14">
         <v>0.1077589236175302</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2B14</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:17">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15">
         <v>-0.07620363227381255</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>-0.06813763098470348</v>
       </c>
-      <c r="D15" t="n">
-        <v>-0.07221435090138531</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15">
+        <v>-0.0722143509013853</v>
+      </c>
+      <c r="E15">
         <v>-0.01404877519019945</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>-0.01407857901184465</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>0.09029425615889389</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>-0.1582584047285658</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>0.01869270672839372</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>-0.1645019021074005</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>-0.02617746932825495</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>-0.1936376179790086</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>-0.0769199549019739</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15">
         <v>0.1372039269607462</v>
       </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
         <v>0.1102396881306789</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15">
         <v>0.05202179735072979</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>2B15</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:17">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
         <v>-0.1799245978185016</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>-0.1122998229373785</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>-0.3212942619212439</v>
       </c>
-      <c r="E16" t="n">
-        <v>1.965406310489524e-05</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="E16">
+        <v>1.965406310489524E-05</v>
+      </c>
+      <c r="F16">
         <v>0.06397483323989694</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>0.1260291270420101</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>-0.2337078150003693</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>-0.1045185577166378</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>-0.1202206837915211</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>-0.2011718146514364</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>-0.1674077273572103</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>-0.04796343970190069</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16">
         <v>-0.0135405021281302</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16">
         <v>0.1102396881306789</v>
       </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
         <v>0.1104162945114745</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>2B16</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:17">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17">
         <v>-0.2396486437927749</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>-0.3371904033451248</v>
       </c>
-      <c r="D17" t="n">
-        <v>-0.02655668163502421</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17">
+        <v>-0.02655668163502419</v>
+      </c>
+      <c r="E17">
         <v>0.2718487653875896</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>-0.05793016085759873</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>-0.2362883730506849</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>-0.07668770031762775</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>-0.06168056662019195</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>-0.1471097055663321</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>0.09734008380018225</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>-0.2750814558494019</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>-0.1031564073434476</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17">
         <v>0.1077589236175302</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17">
         <v>0.05202179735072979</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17">
         <v>0.1104162945114745</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>